--- a/public/templates/13-week-cash-flow-template.xlsx
+++ b/public/templates/13-week-cash-flow-template.xlsx
@@ -422,7 +422,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>From zensus.app. Enter amounts in the input rows; totals, net cash flow, closing balances, and the buffer check are formulas. Week 1 opening balance and the cash buffer floor are the only setup inputs.</v>
+        <v>From zensus.finance. Enter amounts in the input rows; totals, net cash flow, closing balances, and the buffer check are formulas. Week 1 opening balance and the cash buffer floor are the only setup inputs.</v>
       </c>
     </row>
     <row r="4">

--- a/public/templates/13-week-cash-flow-template.xlsx
+++ b/public/templates/13-week-cash-flow-template.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,8 +65,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -473,6 +475,42 @@
       <c r="A5" t="str">
         <v>Week beginning (enter date)</v>
       </c>
+      <c r="C5" s="1">
+        <f>IF(B5="","",B5+7)</f>
+      </c>
+      <c r="D5" s="1">
+        <f>IF(C5="","",C5+7)</f>
+      </c>
+      <c r="E5" s="1">
+        <f>IF(D5="","",D5+7)</f>
+      </c>
+      <c r="F5" s="1">
+        <f>IF(E5="","",E5+7)</f>
+      </c>
+      <c r="G5" s="1">
+        <f>IF(F5="","",F5+7)</f>
+      </c>
+      <c r="H5" s="1">
+        <f>IF(G5="","",G5+7)</f>
+      </c>
+      <c r="I5" s="1">
+        <f>IF(H5="","",H5+7)</f>
+      </c>
+      <c r="J5" s="1">
+        <f>IF(I5="","",I5+7)</f>
+      </c>
+      <c r="K5" s="1">
+        <f>IF(J5="","",J5+7)</f>
+      </c>
+      <c r="L5" s="1">
+        <f>IF(K5="","",K5+7)</f>
+      </c>
+      <c r="M5" s="1">
+        <f>IF(L5="","",L5+7)</f>
+      </c>
+      <c r="N5" s="1">
+        <f>IF(M5="","",M5+7)</f>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
